--- a/docs/sample-blog-platform.xlsx
+++ b/docs/sample-blog-platform.xlsx
@@ -64,7 +64,7 @@
     <t>Заголовок</t>
   </si>
   <si>
-    <t>Slug</t>
+    <t>Адрес публикации</t>
   </si>
   <si>
     <t>Статус</t>
@@ -381,10 +381,10 @@
         <v>22</v>
       </c>
       <c r="F2" t="n" s="2">
-        <v>46263.64716702546</v>
+        <v>46269.675964270835</v>
       </c>
       <c r="G2" t="n" s="2">
-        <v>46264.64716702546</v>
+        <v>46270.675964270835</v>
       </c>
       <c r="H2" t="s" s="0">
         <v>23</v>
@@ -407,10 +407,10 @@
         <v>22</v>
       </c>
       <c r="F3" t="n" s="2">
-        <v>46265.64716702546</v>
+        <v>46271.675964270835</v>
       </c>
       <c r="G3" t="n" s="2">
-        <v>46266.64716702546</v>
+        <v>46272.675964270835</v>
       </c>
       <c r="H3" t="s" s="0">
         <v>26</v>
@@ -433,7 +433,7 @@
         <v>29</v>
       </c>
       <c r="F4" t="n" s="2">
-        <v>46268.64716702546</v>
+        <v>46274.675964270835</v>
       </c>
       <c r="G4" s="0"/>
       <c r="H4" t="s" s="0">
@@ -457,7 +457,7 @@
         <v>33</v>
       </c>
       <c r="F5" t="n" s="2">
-        <v>46271.64716702546</v>
+        <v>46277.675964270835</v>
       </c>
       <c r="G5" s="0"/>
       <c r="H5" t="s" s="0">
@@ -481,10 +481,10 @@
         <v>22</v>
       </c>
       <c r="F6" t="n" s="2">
-        <v>46273.64716702546</v>
+        <v>46279.675964270835</v>
       </c>
       <c r="G6" t="n" s="2">
-        <v>46274.64716702546</v>
+        <v>46280.675964270835</v>
       </c>
       <c r="H6" t="s" s="0">
         <v>37</v>
@@ -507,7 +507,7 @@
         <v>29</v>
       </c>
       <c r="F7" t="n" s="2">
-        <v>46275.64716702546</v>
+        <v>46281.675964270835</v>
       </c>
       <c r="G7" s="0"/>
       <c r="H7" t="s" s="0">
@@ -531,7 +531,7 @@
         <v>33</v>
       </c>
       <c r="F8" t="n" s="2">
-        <v>46276.64716702546</v>
+        <v>46282.675964270835</v>
       </c>
       <c r="G8" s="0"/>
       <c r="H8" t="s" s="0">
@@ -555,10 +555,10 @@
         <v>22</v>
       </c>
       <c r="F9" t="n" s="2">
-        <v>46277.64716702546</v>
+        <v>46283.675964270835</v>
       </c>
       <c r="G9" t="n" s="2">
-        <v>46278.64716702546</v>
+        <v>46284.675964270835</v>
       </c>
       <c r="H9" t="s" s="0">
         <v>46</v>
@@ -581,10 +581,10 @@
         <v>49</v>
       </c>
       <c r="F10" t="n" s="2">
-        <v>46253.64716702546</v>
+        <v>46259.675964270835</v>
       </c>
       <c r="G10" t="n" s="2">
-        <v>46254.64716702546</v>
+        <v>46260.675964270835</v>
       </c>
       <c r="H10" t="s" s="0">
         <v>50</v>
@@ -607,7 +607,7 @@
         <v>33</v>
       </c>
       <c r="F11" t="n" s="2">
-        <v>46281.64716702546</v>
+        <v>46287.675964270835</v>
       </c>
       <c r="G11" s="0"/>
       <c r="H11" t="s" s="0">

--- a/docs/sample-blog-platform.xlsx
+++ b/docs/sample-blog-platform.xlsx
@@ -85,7 +85,7 @@
     <t>blog-platform-architecture</t>
   </si>
   <si>
-    <t>PUBLISHED</t>
+    <t>Опубликована</t>
   </si>
   <si>
     <t>Обзор основных слоев приложения и их ответственности.</t>
@@ -106,7 +106,7 @@
     <t>java-collections</t>
   </si>
   <si>
-    <t>REVIEW</t>
+    <t>На проверке</t>
   </si>
   <si>
     <t>Фильтрация и сортировка публикаций с использованием Stream API.</t>
@@ -118,7 +118,7 @@
     <t>postgresql-draft</t>
   </si>
   <si>
-    <t>DRAFT</t>
+    <t>Черновик</t>
   </si>
   <si>
     <t>Заметки о проектировании таблиц и ограничений.</t>
@@ -166,7 +166,7 @@
     <t>first-platform-version</t>
   </si>
   <si>
-    <t>ARCHIVED</t>
+    <t>В архиве</t>
   </si>
   <si>
     <t>Архивная публикация о первой версии проекта.</t>
@@ -332,7 +332,7 @@
     <col min="2" max="2" width="10.91015625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="28.37109375" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="23.88671875" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="11.1328125" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="14.25390625" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="16.90234375" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="16.90234375" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="60.0" customWidth="true" bestFit="true"/>

--- a/docs/sample-blog-platform.xlsx
+++ b/docs/sample-blog-platform.xlsx
@@ -8,16 +8,18 @@
   <sheets>
     <sheet name="Авторы" r:id="rId3" sheetId="1"/>
     <sheet name="Публикации" r:id="rId4" sheetId="2"/>
+    <sheet name="Комментарии" r:id="rId5" sheetId="3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">Авторы!$A$1:$C$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">Авторы!$A$1:$D$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Публикации!$A$1:$H$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="true">Комментарии!$A$1:$F$6</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="65">
   <si>
     <t>ID</t>
   </si>
@@ -28,12 +30,18 @@
     <t>Email</t>
   </si>
   <si>
+    <t>Роль</t>
+  </si>
+  <si>
     <t>Максим Изосимов</t>
   </si>
   <si>
     <t>maxim@example.com</t>
   </si>
   <si>
+    <t>Автор</t>
+  </si>
+  <si>
     <t>Никита Абаляев</t>
   </si>
   <si>
@@ -148,7 +156,7 @@
     <t>unique-slugs</t>
   </si>
   <si>
-    <t>Зачем публикациям нужен уникальный slug.</t>
+    <t>Зачем публикациям нужен уникальный адрес.</t>
   </si>
   <si>
     <t>Архитектура Repository</t>
@@ -179,6 +187,33 @@
   </si>
   <si>
     <t>Список ключевых решений, которые нужно объяснить на защите.</t>
+  </si>
+  <si>
+    <t>ID публикации</t>
+  </si>
+  <si>
+    <t>Текст</t>
+  </si>
+  <si>
+    <t>Хорошо показано разделение слоёв.</t>
+  </si>
+  <si>
+    <t>Одобрен</t>
+  </si>
+  <si>
+    <t>Подскажите, зачем нужен PreparedStatement?</t>
+  </si>
+  <si>
+    <t>Пример сортировки очень полезен.</t>
+  </si>
+  <si>
+    <t>Где находится полученный файл?</t>
+  </si>
+  <si>
+    <t>Комментарий для проверки отклонения.</t>
+  </si>
+  <si>
+    <t>Отклонён</t>
   </si>
 </sst>
 </file>
@@ -243,12 +278,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="4.7421875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="17.703125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="19.8046875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="7.5703125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -261,16 +297,22 @@
       <c r="C1" t="s" s="1">
         <v>2</v>
       </c>
+      <c r="D1" t="s" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -278,9 +320,12 @@
         <v>2.0</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s" s="0">
         <v>6</v>
       </c>
     </row>
@@ -289,10 +334,13 @@
         <v>3.0</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>8</v>
+        <v>10</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -300,10 +348,13 @@
         <v>4.0</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -311,14 +362,17 @@
         <v>5.0</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>12</v>
+        <v>14</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C6"/>
+  <autoFilter ref="A1:D6"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
@@ -343,25 +397,25 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2">
@@ -372,22 +426,22 @@
         <v>1.0</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F2" t="n" s="2">
-        <v>46269.675964270835</v>
+        <v>46280.54559310185</v>
       </c>
       <c r="G2" t="n" s="2">
-        <v>46270.675964270835</v>
+        <v>46281.54559310185</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -398,22 +452,22 @@
         <v>2.0</v>
       </c>
       <c r="C3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="D3" t="s" s="0">
-        <v>25</v>
-      </c>
-      <c r="E3" t="s" s="0">
-        <v>22</v>
-      </c>
       <c r="F3" t="n" s="2">
-        <v>46271.675964270835</v>
+        <v>46282.54559310185</v>
       </c>
       <c r="G3" t="n" s="2">
-        <v>46272.675964270835</v>
+        <v>46283.54559310185</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -424,20 +478,20 @@
         <v>3.0</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F4" t="n" s="2">
-        <v>46274.675964270835</v>
+        <v>46285.54559310185</v>
       </c>
       <c r="G4" s="0"/>
       <c r="H4" t="s" s="0">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
@@ -448,20 +502,20 @@
         <v>4.0</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F5" t="n" s="2">
-        <v>46277.675964270835</v>
+        <v>46288.54559310185</v>
       </c>
       <c r="G5" s="0"/>
       <c r="H5" t="s" s="0">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
@@ -472,22 +526,22 @@
         <v>5.0</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F6" t="n" s="2">
-        <v>46279.675964270835</v>
+        <v>46290.54559310185</v>
       </c>
       <c r="G6" t="n" s="2">
-        <v>46280.675964270835</v>
+        <v>46291.54559310185</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
@@ -498,20 +552,20 @@
         <v>1.0</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F7" t="n" s="2">
-        <v>46281.675964270835</v>
+        <v>46292.54559310185</v>
       </c>
       <c r="G7" s="0"/>
       <c r="H7" t="s" s="0">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8">
@@ -522,20 +576,20 @@
         <v>2.0</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F8" t="n" s="2">
-        <v>46282.675964270835</v>
+        <v>46293.54559310185</v>
       </c>
       <c r="G8" s="0"/>
       <c r="H8" t="s" s="0">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9">
@@ -546,22 +600,22 @@
         <v>3.0</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E9" t="s" s="0">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F9" t="n" s="2">
-        <v>46283.675964270835</v>
+        <v>46294.54559310185</v>
       </c>
       <c r="G9" t="n" s="2">
-        <v>46284.675964270835</v>
+        <v>46295.54559310185</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
@@ -572,22 +626,22 @@
         <v>4.0</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E10" t="s" s="0">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F10" t="n" s="2">
-        <v>46259.675964270835</v>
+        <v>46270.54559310185</v>
       </c>
       <c r="G10" t="n" s="2">
-        <v>46260.675964270835</v>
+        <v>46271.54559310185</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11">
@@ -598,24 +652,163 @@
         <v>5.0</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F11" t="n" s="2">
-        <v>46287.675964270835</v>
+        <v>46298.54559310185</v>
       </c>
       <c r="G11" s="0"/>
       <c r="H11" t="s" s="0">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H11"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="4.7421875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="15.41015625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.91015625" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="60.0" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="12.87109375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="16.90234375" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>56</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>57</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="B2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="F2" t="n" s="2">
+        <v>46282.54559310185</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="B3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="F3" t="n" s="2">
+        <v>46284.54559310185</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="B4" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="F4" t="n" s="2">
+        <v>46287.54559310185</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="B5" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="F5" t="n" s="2">
+        <v>46292.54559310185</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="B6" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="F6" t="n" s="2">
+        <v>46296.54559310185</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F6"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>